--- a/artfynd/A 9124-2020 artfynd.xlsx
+++ b/artfynd/A 9124-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121073575</v>
+        <v>121073571</v>
       </c>
       <c r="B2" t="n">
-        <v>58205</v>
+        <v>58216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121073573</v>
+        <v>121073575</v>
       </c>
       <c r="B3" t="n">
-        <v>58216</v>
+        <v>58208</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100141</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072897</v>
+        <v>121073573</v>
       </c>
       <c r="B4" t="n">
-        <v>58177</v>
+        <v>58219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>100141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,20 +945,24 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stråvalla, Hl</t>
+          <t>Holmas, anlagd damm, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332443</v>
+        <v>332302</v>
       </c>
       <c r="R4" t="n">
-        <v>6353038</v>
+        <v>6352955</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,17 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stora samlingar yngel</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,14 +1015,18 @@
           <t>Elsa Fogelström, Erik Lagerin</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering, WSP Sverige AB</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121073571</v>
+        <v>121072897</v>
       </c>
       <c r="B5" t="n">
-        <v>58213</v>
+        <v>58180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,16 +1039,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1058,24 +1061,20 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmas, anlagd damm, Hl</t>
+          <t>Stråvalla, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>332302</v>
+        <v>332443</v>
       </c>
       <c r="R5" t="n">
-        <v>6352955</v>
+        <v>6353038</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,12 +1098,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stora samlingar yngel</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,11 +1132,7 @@
           <t>Elsa Fogelström, Erik Lagerin</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering, WSP Sverige AB</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9124-2020 artfynd.xlsx
+++ b/artfynd/A 9124-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121073571</v>
+        <v>121073573</v>
       </c>
       <c r="B2" t="n">
-        <v>58216</v>
+        <v>58219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121073573</v>
+        <v>121072897</v>
       </c>
       <c r="B4" t="n">
-        <v>58219</v>
+        <v>58180</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100141</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,24 +945,20 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmas, anlagd damm, Hl</t>
+          <t>Stråvalla, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332302</v>
+        <v>332443</v>
       </c>
       <c r="R4" t="n">
-        <v>6352955</v>
+        <v>6353038</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,12 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stora samlingar yngel</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,18 +1016,14 @@
           <t>Elsa Fogelström, Erik Lagerin</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering, WSP Sverige AB</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072897</v>
+        <v>121073571</v>
       </c>
       <c r="B5" t="n">
-        <v>58180</v>
+        <v>58216</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,16 +1036,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,20 +1058,24 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stråvalla, Hl</t>
+          <t>Holmas, anlagd damm, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>332443</v>
+        <v>332302</v>
       </c>
       <c r="R5" t="n">
-        <v>6353038</v>
+        <v>6352955</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,17 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stora samlingar yngel</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1128,11 @@
           <t>Elsa Fogelström, Erik Lagerin</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering, WSP Sverige AB</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
